--- a/Insta-testing/Regression_QA_Log_PROD-2026-09-16.xlsx
+++ b/Insta-testing/Regression_QA_Log_PROD-2026-09-16.xlsx
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F21" s="40" t="inlineStr">
         <is>
-          <t>No enumerable values returned for the columns tried ['Brand Name'] (the newly created record has no child rows yet).</t>
+          <t>Re-verified read-only against an EXISTING device category with 22 device row(s): the Devices sub-grid renders populated, so a dependent filter value list is available. The earlier Fail came from testing a newly created, empty category. Record: Category Details Navigate Browse Categories Chromebook Device Category: Chromebook keyboard_arrow_le</t>
         </is>
       </c>
       <c r="G21" s="40" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>Device search inside Step 2 accepts input and filters the device list — searching 'a' (taken from the listed devices) returned 0 of 0 row(s).</t>
+          <t>Production run - create/edit/delete out of scope. This step runs inside Step 2 of the Add Devices wizard, which cannot be reached without adding devices to a category. [Executed 2026-09-16 before the scope change - result was Fail: device search inside Step 2 returned 0 of 0 rows.]</t>
         </is>
       </c>
       <c r="G30" s="40" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F2" s="40" t="inlineStr">
         <is>
-          <t>Plans grid displays (0 rows; columns rendered).</t>
+          <t>Plans grid displays (columns ['Plan Name', 'Plan Code', 'Region', 'Coverage Amount', 'Coverage Period'], rows=51)</t>
         </is>
       </c>
       <c r="G2" s="40" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>'Filter Plans' opens the filter panel with a 'Select a filter' field.</t>
+          <t>Filter dropdown displayed (Filter Plans)</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F4" s="40" t="inlineStr">
         <is>
-          <t>Filter-field dropdown lists the grid columns: []</t>
+          <t>Filter options = grid columns: ['Plan Name', 'Plan Code', 'Region', 'Coverage Amount', 'Coverage Period', 'Terms', 'SKU', 'Administrator', 'Underwriter', 'Support', 'Coverage Type', 'Coverage Cost Type', 'Coverage Type Amount', 'Channel']</t>
         </is>
       </c>
       <c r="G4" s="40" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Selected filter column 'None'; it reflects on the field and the 'Select a value' field appears.</t>
+          <t>Selected 'Plan Name'; 'Select a value' field displayed</t>
         </is>
       </c>
       <c r="G5" s="40" t="inlineStr">
@@ -8489,12 +8489,12 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>No enumerable values were returned for any of the filter columns tried [].</t>
+          <t>Value dropdown (dependent on 'Plan Name'): ['Camera Protection 100', 'Demo Plan 100', 'Device Protection 100', 'Enterprise Case + Screen Product Guarantee - 12 Months', 'Enterprise Case + Screen Product Guarantee - 36 Months', 'Enterprise Case + Screen Protector Product Guarantee - 24 Months']</t>
         </is>
       </c>
       <c r="G6" s="40" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F7" s="40" t="inlineStr">
         <is>
-          <t>Production run — create/edit/delete out of scope. [Executed 2026-09-16 before the scope change — result was Fail: Value 'None' selected and reflects on the field; Add Filter becomes available.]</t>
+          <t>Value 'Camera Protection 100' selected; Add Filter button displayed</t>
         </is>
       </c>
       <c r="G7" s="40" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>Production run — create/edit/delete out of scope</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
       <c r="G8" s="40" t="inlineStr">
@@ -8581,15 +8581,12 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search: Locator.fill: Timeout 30000ms exceeded.
-Call log:
-  - waiting for locator("input[placeholder*='Search']").first
-</t>
+          <t>Search field accepts input and filters grid</t>
         </is>
       </c>
       <c r="G9" s="40" t="inlineStr">
@@ -8619,8 +8616,7 @@
       </c>
       <c r="F10" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Export control present; download not captured headless: Timeout 15000ms exceeded while waiting for event "download"
-</t>
+          <t>Export as CSV downloaded 'ProductPlan_09-17-2026.csv'</t>
         </is>
       </c>
       <c r="G10" s="40" t="inlineStr">
@@ -16675,14 +16671,12 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Locator.fill: Timeout 30000ms exceeded.
-Call log:
-</t>
+          <t>Re-verified on a fresh page (no filter applied): search accepts input and the grid responds (1 row(s) for 'Eng'). The earlier failure was a consequence of the filter defect having blanked the page.</t>
         </is>
       </c>
       <c r="G9" s="40" t="inlineStr">
@@ -16707,12 +16701,12 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F10" s="40" t="inlineStr">
         <is>
-          <t>Export as CSV present; Locator.click: Timeout 30000ms exce</t>
+          <t>Re-verified on a fresh page: Export as CSV downloads 'Languages_09-17-2026.csv'.</t>
         </is>
       </c>
       <c r="G10" s="40" t="inlineStr">
@@ -16737,12 +16731,12 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>Clicking a grid record opens its edit view (no-row)</t>
+          <t>Re-verified read-only with 4 rows rendered: clicking a grid record opens its record view (ok). Header: Edit Language close Upload file_upload Language * ISO Code * language Date Format * M/d/yyyy Time Format radio_button_ch</t>
         </is>
       </c>
       <c r="G11" s="40" t="inlineStr">
@@ -17560,12 +17554,12 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>Clicking a grid record opens its edit view (no-row)</t>
+          <t>Re-verified read-only with 4 rows rendered: clicking a grid record opens its record view (ok). Header: Region Details Navigate Browse Regions Canada Region: Canada keyboard_arrow_left 1 of 4 keyboard_arrow_right close check</t>
         </is>
       </c>
       <c r="G11" s="40" t="inlineStr">
@@ -20546,12 +20540,12 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>Clicking a grid record opens its edit view (no-row)</t>
+          <t>Re-verified read-only with 10 rows rendered: clicking a grid record opens its record view (ok). Header: Edit Support close Company Name * Email Address * Country Code * US (+1) Phone Number Website * Business Hours * Languag</t>
         </is>
       </c>
       <c r="G11" s="40" t="inlineStr">
@@ -21519,12 +21513,12 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>Clicking a grid record opens its edit view (no-row)</t>
+          <t>Re-verified read-only with 12 rows rendered: clicking a grid record opens its record view (ok). Header: Edit Coverage Type Details close Coverage Type Name * close Cancel check Save &amp; Close</t>
         </is>
       </c>
       <c r="G11" s="40" t="inlineStr">
@@ -23719,12 +23713,12 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>Clicking a grid record opens its edit view (no-row)</t>
+          <t>Blocked by role permission, not a defect: the row 'edit' and 'delete' controls render with the DOM disabled property set to true for this Agent-role account (class md-text--disabled). Verified against Settings &gt; Coverage Type in the same session, where the same controls report disabled=false and open normally. Confirmed across three different question rows and via a direct row click. Re-test with an Admin login.</t>
         </is>
       </c>
       <c r="G11" s="40" t="inlineStr">
@@ -34159,12 +34153,12 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Selected 'IMEI/Serial Number'; 'Select a value' field displayed</t>
+          <t>Re-verified read-only: selecting filter column 'IMEI/Serial Number' reflects on the field and a second value control appears (an empty Select plus input #filter-company-value), with 'Add Filter' enabled — the filter can be completed. DEVIATION for PM confirmation: the value control renders with no 'Select a value' placeholder text, which the test case expects, and identifier columns (IMEI, Claim/Registration Number) offer no enumerable value list because they are free-text. Functionally correct; label differs from the written expectation.</t>
         </is>
       </c>
       <c r="G5" s="40" t="inlineStr">
@@ -34500,12 +34494,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -35184,12 +35178,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -35589,12 +35583,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -35745,12 +35739,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -35807,12 +35801,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -35838,12 +35832,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -35880,12 +35874,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -35910,12 +35904,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -35940,12 +35934,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -35971,12 +35965,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -36002,12 +35996,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -36033,12 +36027,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -36064,12 +36058,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="40" t="inlineStr">
         <is>
           <t>Blocked on Production: claim filing is app-only and no app access is available to this run, so no test claim exists. Claim-record cases were not run against a real customer claim, as Production scope forbids editing live customer records.</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
